--- a/assets/fonte/planilha input - DRO_5050_teste_XML.xlsx
+++ b/assets/fonte/planilha input - DRO_5050_teste_XML.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\conversor_dro_5050 3\assets\fonte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318BEDB1-7E83-4361-8586-7F7249C2E9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39831F4-19C2-4FE7-B541-7BE732BE6D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27000" yWindow="3855" windowWidth="21375" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25725" yWindow="3255" windowWidth="24675" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -362,7 +362,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -373,12 +373,8 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial Unicode MS"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,11 +399,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -503,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -544,13 +535,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -560,17 +544,11 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -881,10 +859,10 @@
       <c r="F2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="14">
         <v>45996</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="14">
         <v>45981</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -920,22 +898,22 @@
       <c r="S2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="19">
+      <c r="T2" s="16">
         <v>8000000</v>
       </c>
-      <c r="U2" s="17">
+      <c r="U2" s="14">
         <v>46001</v>
       </c>
       <c r="V2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="6" t="s">
         <v>53</v>
       </c>
       <c r="X2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="Y2" s="6" t="s">
         <v>55</v>
       </c>
       <c r="Z2" s="6" t="s">
@@ -944,13 +922,13 @@
       <c r="AA2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AB2" s="19">
+      <c r="AB2" s="16">
         <v>1200</v>
       </c>
-      <c r="AC2" s="19">
+      <c r="AC2" s="16">
         <v>0</v>
       </c>
-      <c r="AD2" s="19">
+      <c r="AD2" s="16">
         <v>0</v>
       </c>
       <c r="AE2" s="6" t="s">
@@ -976,10 +954,10 @@
       <c r="F3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="14">
         <v>45996</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="14">
         <v>45981</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -1015,22 +993,22 @@
       <c r="S3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="T3" s="19">
+      <c r="T3" s="16">
         <v>4000000</v>
       </c>
-      <c r="U3" s="17">
+      <c r="U3" s="14">
         <v>46068</v>
       </c>
       <c r="V3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="14" t="s">
+      <c r="W3" s="6" t="s">
         <v>53</v>
       </c>
       <c r="X3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="14" t="s">
+      <c r="Y3" s="6" t="s">
         <v>55</v>
       </c>
       <c r="Z3" s="6" t="s">
@@ -1039,13 +1017,13 @@
       <c r="AA3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AB3" s="19">
+      <c r="AB3" s="16">
         <v>300</v>
       </c>
-      <c r="AC3" s="19">
+      <c r="AC3" s="16">
         <v>500</v>
       </c>
-      <c r="AD3" s="19">
+      <c r="AD3" s="16">
         <v>0</v>
       </c>
       <c r="AE3" s="6" t="s">
@@ -1071,10 +1049,10 @@
       <c r="F4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="14">
         <v>45996</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="14">
         <v>45981</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -1108,20 +1086,20 @@
         <v>50</v>
       </c>
       <c r="S4" s="6"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="17">
+      <c r="T4" s="16"/>
+      <c r="U4" s="14">
         <v>46132</v>
       </c>
       <c r="V4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="14" t="s">
+      <c r="W4" s="6" t="s">
         <v>53</v>
       </c>
       <c r="X4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Y4" s="14" t="s">
+      <c r="Y4" s="6" t="s">
         <v>55</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1130,13 +1108,13 @@
       <c r="AA4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AB4" s="19">
+      <c r="AB4" s="16">
         <v>0</v>
       </c>
-      <c r="AC4" s="19">
+      <c r="AC4" s="16">
         <v>0</v>
       </c>
-      <c r="AD4" s="19">
+      <c r="AD4" s="16">
         <v>-200</v>
       </c>
       <c r="AE4" s="6" t="s">
@@ -1157,19 +1135,19 @@
         <v>62</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="14">
         <v>46030</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="14">
         <v>46028</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>65</v>
@@ -1198,36 +1176,36 @@
       <c r="R5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S5" s="16"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="17">
+      <c r="S5" s="6"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="14">
         <v>46032</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="V5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="W5" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="X5" s="22" t="s">
+      <c r="X5" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="Z5" s="22" t="s">
+      <c r="Z5" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="AA5" s="22" t="s">
+      <c r="AA5" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="AB5" s="24">
-        <v>2500</v>
-      </c>
-      <c r="AC5" s="24">
-        <v>300</v>
-      </c>
-      <c r="AD5" s="19">
+      <c r="AB5" s="19">
+        <v>1800</v>
+      </c>
+      <c r="AC5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="16">
         <v>0</v>
       </c>
       <c r="AE5" s="6" t="s">
@@ -1253,10 +1231,10 @@
       <c r="F6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="14">
         <v>45966</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="14">
         <v>45962</v>
       </c>
       <c r="I6" s="6" t="s">
@@ -1290,20 +1268,20 @@
         <v>50</v>
       </c>
       <c r="S6" s="6"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="17">
+      <c r="T6" s="16"/>
+      <c r="U6" s="14">
         <v>45971</v>
       </c>
       <c r="V6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="W6" s="14" t="s">
+      <c r="W6" s="6" t="s">
         <v>79</v>
       </c>
       <c r="X6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="Y6" s="14" t="s">
+      <c r="Y6" s="6" t="s">
         <v>81</v>
       </c>
       <c r="Z6" s="6" t="s">
@@ -1312,13 +1290,13 @@
       <c r="AA6" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="AB6" s="19">
+      <c r="AB6" s="16">
         <v>400</v>
       </c>
-      <c r="AC6" s="19">
+      <c r="AC6" s="16">
         <v>0</v>
       </c>
-      <c r="AD6" s="19">
+      <c r="AD6" s="16">
         <v>0</v>
       </c>
       <c r="AE6" s="6" t="s">
@@ -1344,10 +1322,10 @@
       <c r="F7" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="14">
         <v>45966</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="14">
         <v>45962</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -1381,20 +1359,20 @@
         <v>50</v>
       </c>
       <c r="S7" s="6"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="17">
+      <c r="T7" s="16"/>
+      <c r="U7" s="14">
         <v>46091</v>
       </c>
       <c r="V7" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="W7" s="6" t="s">
         <v>79</v>
       </c>
       <c r="X7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="Y7" s="14" t="s">
+      <c r="Y7" s="6" t="s">
         <v>81</v>
       </c>
       <c r="Z7" s="6" t="s">
@@ -1403,13 +1381,13 @@
       <c r="AA7" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="AB7" s="19">
+      <c r="AB7" s="16">
         <v>300</v>
       </c>
-      <c r="AC7" s="19">
+      <c r="AC7" s="16">
         <v>0</v>
       </c>
-      <c r="AD7" s="19">
+      <c r="AD7" s="16">
         <v>0</v>
       </c>
       <c r="AE7" s="6" t="s">
@@ -1435,10 +1413,10 @@
       <c r="F8" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="15">
         <v>46055</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="15">
         <v>46050</v>
       </c>
       <c r="I8" s="7" t="s">
@@ -1472,20 +1450,20 @@
         <v>50</v>
       </c>
       <c r="S8" s="7"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="18">
+      <c r="T8" s="17"/>
+      <c r="U8" s="15">
         <v>46058</v>
       </c>
       <c r="V8" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="6" t="s">
         <v>93</v>
       </c>
       <c r="X8" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="Y8" s="15" t="s">
+      <c r="Y8" s="6" t="s">
         <v>95</v>
       </c>
       <c r="Z8" s="7" t="s">
@@ -1494,13 +1472,13 @@
       <c r="AA8" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AB8" s="21">
+      <c r="AB8" s="17">
         <v>900</v>
       </c>
-      <c r="AC8" s="21">
+      <c r="AC8" s="17">
         <v>0</v>
       </c>
-      <c r="AD8" s="21">
+      <c r="AD8" s="17">
         <v>0</v>
       </c>
       <c r="AE8" s="7" t="s">

--- a/assets/fonte/planilha input - DRO_5050_teste_XML.xlsx
+++ b/assets/fonte/planilha input - DRO_5050_teste_XML.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\conversor_dro_5050 3\assets\fonte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39831F4-19C2-4FE7-B541-7BE732BE6D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB8DC9F-E35E-41FC-A099-2FC69CC5B421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25725" yWindow="3255" windowWidth="24675" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24840" yWindow="4140" windowWidth="24675" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -151,208 +151,208 @@
     <t>41 - Adequacao de produto a cliente</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>CIV - Civel</t>
+  </si>
+  <si>
+    <t>JURID001</t>
+  </si>
+  <si>
+    <t>Sistema juridico de contingencias</t>
+  </si>
+  <si>
+    <t>PROC000001</t>
+  </si>
+  <si>
+    <t>Contingencia civel avaliada individualmente com perda provisao e duas probabilidades.</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Z1234567</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>819951030000000000000001</t>
+  </si>
+  <si>
+    <t>Conta debito contingencia civel</t>
+  </si>
+  <si>
+    <t>499353000900000000000001</t>
+  </si>
+  <si>
+    <t>Conta credito contingencia civel</t>
+  </si>
+  <si>
+    <t>8199510300</t>
+  </si>
+  <si>
+    <t>4993530009</t>
+  </si>
+  <si>
+    <t>RE</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>IND0002</t>
+  </si>
+  <si>
+    <t>7 - Falhas em sistemas processos ou infraestrutura de tecnologia da informacao</t>
+  </si>
+  <si>
+    <t>71 - Falhas em sistemas processos ou infraestrutura de TI</t>
+  </si>
+  <si>
+    <t>NA - Nao se aplica</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>SISTTI001</t>
+  </si>
+  <si>
+    <t>Sistema de tecnologia da informacao</t>
+  </si>
+  <si>
+    <t>INCIDENTE001</t>
+  </si>
+  <si>
+    <t>Falha de tecnologia com perda individualizada superior ao limiar de identificacao.</t>
+  </si>
+  <si>
+    <t>CONS0001</t>
+  </si>
+  <si>
+    <t>1 - Fraudes internas</t>
+  </si>
+  <si>
+    <t>11 - Atividade nao autorizada</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>FRAUIN01</t>
+  </si>
+  <si>
+    <t>Sistema de fraudes internas</t>
+  </si>
+  <si>
+    <t>FRAUDEINT001</t>
+  </si>
+  <si>
+    <t>Evento de fraude interna abaixo do limiar para consolidacao.</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>810000000000000000000003</t>
+  </si>
+  <si>
+    <t>Conta debito fraude interna</t>
+  </si>
+  <si>
+    <t>410000000000000000000003</t>
+  </si>
+  <si>
+    <t>Conta credito fraude interna</t>
+  </si>
+  <si>
+    <t>10000007</t>
+  </si>
+  <si>
+    <t>20000006</t>
+  </si>
+  <si>
+    <t>CONS0002</t>
+  </si>
+  <si>
+    <t>2 - Fraudes externas</t>
+  </si>
+  <si>
+    <t>21 - Roubo e fraude origem externa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>FRAUEX01</t>
+  </si>
+  <si>
+    <t>Sistema de fraudes externas</t>
+  </si>
+  <si>
+    <t>FRAUDEEXT001</t>
+  </si>
+  <si>
+    <t>Evento de fraude externa abaixo do limiar para consolidacao.</t>
+  </si>
+  <si>
+    <t>810000000000000000000004</t>
+  </si>
+  <si>
+    <t>Conta debito fraude externa</t>
+  </si>
+  <si>
+    <t>410000000000000000000004</t>
+  </si>
+  <si>
+    <t>Conta credito fraude externa</t>
+  </si>
+  <si>
+    <t>11000008</t>
+  </si>
+  <si>
+    <t>21000007</t>
+  </si>
+  <si>
+    <t>5050</t>
+  </si>
+  <si>
+    <t>39151658</t>
+  </si>
+  <si>
+    <t>810000000000000000000002</t>
+  </si>
+  <si>
+    <t>Conta debito falha tecnologia</t>
+  </si>
+  <si>
+    <t>410000000000000000000002</t>
+  </si>
+  <si>
+    <t>Conta credito falha tecnologia</t>
+  </si>
+  <si>
+    <t>12000007</t>
+  </si>
+  <si>
+    <t>41000008</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>C0099999</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
     <t>I - Individual</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>CIV - Civel</t>
-  </si>
-  <si>
-    <t>JURID001</t>
-  </si>
-  <si>
-    <t>Sistema juridico de contingencias</t>
-  </si>
-  <si>
-    <t>PROC000001</t>
-  </si>
-  <si>
-    <t>Contingencia civel avaliada individualmente com perda provisao e duas probabilidades.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Z1234567</t>
-  </si>
-  <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>819951030000000000000001</t>
-  </si>
-  <si>
-    <t>Conta debito contingencia civel</t>
-  </si>
-  <si>
-    <t>499353000900000000000001</t>
-  </si>
-  <si>
-    <t>Conta credito contingencia civel</t>
-  </si>
-  <si>
-    <t>8199510300</t>
-  </si>
-  <si>
-    <t>4993530009</t>
-  </si>
-  <si>
-    <t>RE</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>IND0002</t>
-  </si>
-  <si>
-    <t>7 - Falhas em sistemas processos ou infraestrutura de tecnologia da informacao</t>
-  </si>
-  <si>
-    <t>71 - Falhas em sistemas processos ou infraestrutura de TI</t>
-  </si>
-  <si>
-    <t>NA - Nao se aplica</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>SISTTI001</t>
-  </si>
-  <si>
-    <t>Sistema de tecnologia da informacao</t>
-  </si>
-  <si>
-    <t>INCIDENTE001</t>
-  </si>
-  <si>
-    <t>Falha de tecnologia com perda individualizada superior ao limiar de identificacao.</t>
-  </si>
-  <si>
-    <t>CONS0001</t>
-  </si>
-  <si>
-    <t>1 - Fraudes internas</t>
-  </si>
-  <si>
-    <t>11 - Atividade nao autorizada</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>FRAUIN01</t>
-  </si>
-  <si>
-    <t>Sistema de fraudes internas</t>
-  </si>
-  <si>
-    <t>FRAUDEINT001</t>
-  </si>
-  <si>
-    <t>Evento de fraude interna abaixo do limiar para consolidacao.</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>810000000000000000000003</t>
-  </si>
-  <si>
-    <t>Conta debito fraude interna</t>
-  </si>
-  <si>
-    <t>410000000000000000000003</t>
-  </si>
-  <si>
-    <t>Conta credito fraude interna</t>
-  </si>
-  <si>
-    <t>10000007</t>
-  </si>
-  <si>
-    <t>20000006</t>
-  </si>
-  <si>
-    <t>CONS0002</t>
-  </si>
-  <si>
-    <t>2 - Fraudes externas</t>
-  </si>
-  <si>
-    <t>21 - Roubo e fraude origem externa</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>FRAUEX01</t>
-  </si>
-  <si>
-    <t>Sistema de fraudes externas</t>
-  </si>
-  <si>
-    <t>FRAUDEEXT001</t>
-  </si>
-  <si>
-    <t>Evento de fraude externa abaixo do limiar para consolidacao.</t>
-  </si>
-  <si>
-    <t>810000000000000000000004</t>
-  </si>
-  <si>
-    <t>Conta debito fraude externa</t>
-  </si>
-  <si>
-    <t>410000000000000000000004</t>
-  </si>
-  <si>
-    <t>Conta credito fraude externa</t>
-  </si>
-  <si>
-    <t>11000008</t>
-  </si>
-  <si>
-    <t>21000007</t>
-  </si>
-  <si>
-    <t>5050</t>
-  </si>
-  <si>
-    <t>2026-06</t>
-  </si>
-  <si>
-    <t>39151658</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>C0099999</t>
-  </si>
-  <si>
-    <t>810000000000000000000002</t>
-  </si>
-  <si>
-    <t>Conta debito falha tecnologia</t>
-  </si>
-  <si>
-    <t>410000000000000000000002</t>
-  </si>
-  <si>
-    <t>Conta credito falha tecnologia</t>
-  </si>
-  <si>
-    <t>12000007</t>
-  </si>
-  <si>
-    <t>41000008</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
   <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="33.5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
@@ -854,10 +854,10 @@
         <v>40</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="G2" s="14">
         <v>45996</v>
@@ -866,37 +866,37 @@
         <v>45981</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="L2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="O2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="T2" s="16">
         <v>8000000</v>
@@ -905,22 +905,22 @@
         <v>46001</v>
       </c>
       <c r="V2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="AA2" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="AB2" s="16">
         <v>1200</v>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="38.1" customHeight="1">
@@ -949,10 +949,10 @@
         <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="G3" s="14">
         <v>45996</v>
@@ -961,37 +961,37 @@
         <v>45981</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="L3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="O3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="S3" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T3" s="16">
         <v>4000000</v>
@@ -1000,22 +1000,22 @@
         <v>46068</v>
       </c>
       <c r="V3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="X3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="AB3" s="16">
         <v>300</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="38.1" customHeight="1">
@@ -1044,10 +1044,10 @@
         <v>40</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="G4" s="14">
         <v>45996</v>
@@ -1056,34 +1056,34 @@
         <v>45981</v>
       </c>
       <c r="I4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="L4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="O4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="16"/>
@@ -1091,22 +1091,22 @@
         <v>46132</v>
       </c>
       <c r="V4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="X4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="AA4" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="AB4" s="16">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>-200</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="38.1" customHeight="1">
@@ -1126,19 +1126,19 @@
         <v>37</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G5" s="14">
         <v>46030</v>
@@ -1147,34 +1147,34 @@
         <v>46028</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="L5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="N5" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="S5" s="6"/>
       <c r="T5" s="16"/>
@@ -1182,22 +1182,22 @@
         <v>46032</v>
       </c>
       <c r="V5" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="X5" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="AA5" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="X5" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z5" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA5" s="18" t="s">
-        <v>108</v>
       </c>
       <c r="AB5" s="19">
         <v>1800</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="AE5" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="38.1" customHeight="1">
@@ -1217,19 +1217,19 @@
         <v>37</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="G6" s="14">
         <v>45966</v>
@@ -1238,34 +1238,34 @@
         <v>45962</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="L6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="O6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="S6" s="6"/>
       <c r="T6" s="16"/>
@@ -1273,22 +1273,22 @@
         <v>45971</v>
       </c>
       <c r="V6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="W6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="Z6" s="6" t="s">
+      <c r="AA6" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="AA6" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="AB6" s="16">
         <v>400</v>
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="AE6" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="38.1" customHeight="1">
@@ -1308,19 +1308,19 @@
         <v>37</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="G7" s="14">
         <v>45966</v>
@@ -1329,34 +1329,34 @@
         <v>45962</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="L7" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="M7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="N7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="O7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="S7" s="6"/>
       <c r="T7" s="16"/>
@@ -1364,22 +1364,22 @@
         <v>46091</v>
       </c>
       <c r="V7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="W7" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="Z7" s="6" t="s">
+      <c r="AA7" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="AA7" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="AB7" s="16">
         <v>300</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="38.1" customHeight="1">
@@ -1399,19 +1399,19 @@
         <v>37</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="G8" s="15">
         <v>46055</v>
@@ -1420,34 +1420,34 @@
         <v>46050</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="L8" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="M8" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="N8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="S8" s="7"/>
       <c r="T8" s="17"/>
@@ -1455,22 +1455,22 @@
         <v>46058</v>
       </c>
       <c r="V8" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="W8" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="X8" s="7" t="s">
+      <c r="Y8" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="Z8" s="7" t="s">
+      <c r="AA8" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="AA8" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="AB8" s="17">
         <v>900</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="AE8" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1520,22 +1520,22 @@
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1">
       <c r="A2" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>100</v>
-      </c>
       <c r="E2" s="9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
